--- a/Entrega 3 - Entrega Diciembre/CorregidoIvanSTAGELINK.xlsx
+++ b/Entrega 3 - Entrega Diciembre/CorregidoIvanSTAGELINK.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ivan Alejandro Urso\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Estudios\2025\UAI Tercer Año\Materias primer cuatrimestre, Tercer año\Ingenieria de Software\Entrega 3 - Entrega Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE7D49A4-C667-4EB1-88F1-2C7198D22B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86E0E9C-4A50-4796-B0DB-D9E6A0528315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{2E00496C-2AA8-4611-B3FB-E59896F2425F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E00496C-2AA8-4611-B3FB-E59896F2425F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -649,13 +649,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{796FA2D3-538D-410D-B1B3-104129B4985B}">
   <dimension ref="B1:Y5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="16384" width="8.7265625" style="3"/>
+    <col min="1" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:25" ht="15" thickBot="1"/>
-    <row r="2" spans="2:25" ht="15" thickBot="1">
+    <row r="1" spans="2:25" ht="15.75" thickBot="1"/>
+    <row r="2" spans="2:25" ht="15.75" thickBot="1">
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -687,7 +687,7 @@
       <c r="X2" s="5"/>
       <c r="Y2" s="6"/>
     </row>
-    <row r="3" spans="2:25" ht="26.5" thickBot="1">
+    <row r="3" spans="2:25" ht="26.25" thickBot="1">
       <c r="B3" s="9" t="s">
         <v>3</v>
       </c>
@@ -757,7 +757,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:25" ht="20.5" thickBot="1">
+    <row r="4" spans="2:25" ht="23.25" thickBot="1">
       <c r="B4" s="15" t="s">
         <v>21</v>
       </c>

--- a/Entrega 3 - Entrega Diciembre/CorregidoIvanSTAGELINK.xlsx
+++ b/Entrega 3 - Entrega Diciembre/CorregidoIvanSTAGELINK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Estudios\2025\UAI Tercer Año\Materias primer cuatrimestre, Tercer año\Ingenieria de Software\Entrega 3 - Entrega Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86E0E9C-4A50-4796-B0DB-D9E6A0528315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61409BA9-DF4C-49EF-8549-118E1393EEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E00496C-2AA8-4611-B3FB-E59896F2425F}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
   <si>
     <t>1ra Ent.</t>
   </si>
@@ -197,7 +197,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -280,11 +280,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -333,6 +348,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -761,29 +785,29 @@
       <c r="B4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="C4" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>23</v>
+      <c r="G4" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>22</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>24</v>
@@ -819,13 +843,7 @@
       <c r="F5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>25</v>
       </c>
     </row>
